--- a/backend/data/financials_by_company/002045.SZ.xlsx
+++ b/backend/data/financials_by_company/002045.SZ.xlsx
@@ -3943,187 +3943,187 @@
       </c>
       <c r="DF1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EQ1" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Guoguang Electric Company Limited, together with its subsidiaries, engages in the audio and electroacoustic, and lithium battery businesses in Mainland China, Europe, the United States, and internationally. It operates through Electronic Components Business and Others segments. The company offers speakers, bluetooth speakers, traditional headphones, computer peripheral audio, Wi-Fi speakers, soundbar, AI glasses, AI headphones, VR/AR, car amplifiers, tweeters, subwoofers, musical instrument audio, high-power active speakers, POE speakers, and other products. It also provides lithium battery products for headphones, smart speakers, wearable devices, electronic cigarettes, drones, and other products. In addition, the company is involved in the rental of houses and buildings. Guoguang Electric Company Limited was founded in 1951 and is headquartered in Guangzhou, the People's Republic of China.</t>
+          <t>Guoguang Electric Company Limited, together with its subsidiaries, engages in the audio and electroacoustic, and lithium battery businesses in Mainland China, Europe, the United States, and internationally. The company offers loudspeakers, bluetooth speakers, traditional headphones, computer peripheral audio, Wi-Fi speakers, soundbar, smart speakers, AI glasses, AI headphones, VR/AR products, car amplifiers, AVAS, car speakers, and subwoofers. It also provides lithium battery products for headphones, smart speakers, wearable devices, electronic cigarettes, drones, and other products. In addition, the company is involved in the rental of houses and buildings. Guoguang Electric Company Limited was founded in 1951 and is headquartered in Guangzhou, the People's Republic of China.</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4228,34 +4228,34 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>8.609999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="V2" t="n">
-        <v>8.59</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="X2" t="n">
-        <v>8.779999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.609999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.59</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.779999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AC2" t="n">
         <v>0.02</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="AE2" t="n">
         <v>1780444800</v>
@@ -4267,31 +4267,31 @@
         <v>0.9</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.308</v>
+        <v>0.334</v>
       </c>
       <c r="AI2" t="n">
-        <v>14.114753</v>
+        <v>13.09836</v>
       </c>
       <c r="AJ2" t="n">
-        <v>15728871</v>
+        <v>15496297</v>
       </c>
       <c r="AK2" t="n">
-        <v>15728871</v>
+        <v>15496297</v>
       </c>
       <c r="AL2" t="n">
-        <v>14089426</v>
+        <v>15639156</v>
       </c>
       <c r="AM2" t="n">
-        <v>14142234</v>
+        <v>16495203</v>
       </c>
       <c r="AN2" t="n">
-        <v>14142234</v>
+        <v>16495203</v>
       </c>
       <c r="AO2" t="n">
-        <v>8.630000000000001</v>
+        <v>7.99</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.640000000000001</v>
+        <v>8</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -4300,13 +4300,13 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>4842979840</v>
+        <v>4494240256</v>
       </c>
       <c r="AT2" t="n">
-        <v>4842979766</v>
+        <v>4533614043</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.57</v>
       </c>
       <c r="AV2" t="n">
         <v>19</v>
@@ -4318,19 +4318,19 @@
         <v>2.05096</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.62851304</v>
+        <v>0.5832543</v>
       </c>
       <c r="AZ2" t="n">
-        <v>10.5224</v>
+        <v>9.8596</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.59745</v>
+        <v>13.2123</v>
       </c>
       <c r="BB2" t="n">
         <v>0.015</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.0017421603</v>
+        <v>0.0018987341</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -4341,22 +4341,22 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>6157548032</v>
+        <v>5808808448</v>
       </c>
       <c r="BG2" t="n">
         <v>-0.02219</v>
       </c>
       <c r="BH2" t="n">
-        <v>414505070</v>
+        <v>412783871</v>
       </c>
       <c r="BI2" t="n">
         <v>562483132</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.27741</v>
+        <v>0.27665</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.030840002</v>
+        <v>0.02355</v>
       </c>
       <c r="BL2" t="n">
         <v>562483132</v>
@@ -4365,7 +4365,7 @@
         <v>7.53</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.1434262</v>
+        <v>1.0610889</v>
       </c>
       <c r="BO2" t="n">
         <v>1767139200</v>
@@ -4394,16 +4394,16 @@
         <v>1306454400</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.799</v>
+        <v>0.754</v>
       </c>
       <c r="BX2" t="n">
-        <v>93.51600000000001</v>
+        <v>88.21899999999999</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.4387223</v>
+        <v>-0.49713558</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="CA2" t="n">
         <v>0.015</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>8.609999999999999</v>
+        <v>7.99</v>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
@@ -4516,140 +4516,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DF2" t="b">
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>1783062294</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>finmb_22338267</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DN2" t="b">
         <v>0</v>
       </c>
-      <c r="DG2" t="n">
+      <c r="DO2" t="n">
+        <v>1.1392365</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>Guoguang Electric Company Limited</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>GUOGUANG ELECTRIC COMPANY LIMIT</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
         <v>1116811800000</v>
       </c>
-      <c r="DH2" t="n">
+      <c r="DV2" t="n">
+        <v>0.089999676</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>7.88 - 8.1</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>15639156</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.4199996</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.055482112</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>7.57 - 19.0</t>
+        </is>
+      </c>
+      <c r="EC2" t="n">
+        <v>-11.01</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.5794737</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-49.71356</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>1619693940</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1619693940</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-1.8696003</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.18962233</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>-5.2223005</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-0.3952605</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EP2" t="b">
         <v>0</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>8.2 - 8.78</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DK2" t="n">
-        <v>14089426</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.40999985</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.049999982</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>8.2 - 19.0</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>-10.39</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.5468421</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-43.87223</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1619693940</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1619693940</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>GUOGUANG ELECTRIC COMPANY LIMIT</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>1782111888</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>finmb_22338267</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="EE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-1.9124002</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.18174563</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-4.9874506</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.36679307</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>Guoguang Electric Company Limited</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>8.609999999999999</v>
       </c>
       <c r="EQ2" t="inlineStr"/>
     </row>
